--- a/artfynd/A 4831-2021 artfynd.xlsx
+++ b/artfynd/A 4831-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119961521</v>
+        <v>119961524</v>
       </c>
       <c r="B2" t="n">
         <v>56233</v>
@@ -715,12 +715,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>gående/springande</t>
+          <t>trafikdödad</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">

--- a/artfynd/A 4831-2021 artfynd.xlsx
+++ b/artfynd/A 4831-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119961524</v>
+        <v>119961521</v>
       </c>
       <c r="B2" t="n">
-        <v>56233</v>
+        <v>56243</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,12 +715,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>trafikdödad</t>
+          <t>gående/springande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">

--- a/artfynd/A 4831-2021 artfynd.xlsx
+++ b/artfynd/A 4831-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119961521</v>
+        <v>119961524</v>
       </c>
       <c r="B2" t="n">
         <v>56243</v>
@@ -715,12 +715,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>gående/springande</t>
+          <t>trafikdödad</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">

--- a/artfynd/A 4831-2021 artfynd.xlsx
+++ b/artfynd/A 4831-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119961524</v>
+        <v>119961521</v>
       </c>
       <c r="B2" t="n">
         <v>56243</v>
@@ -715,12 +715,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>trafikdödad</t>
+          <t>gående/springande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
